--- a/exports/trend_1d/RELIANCE_full_report.xlsx
+++ b/exports/trend_1d/RELIANCE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42055</v>
+        <v>42058</v>
       </c>
       <c r="H2" t="n">
-        <v>208.05</v>
+        <v>202.9</v>
       </c>
       <c r="I2" t="n">
         <v>206.8041369011315</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K2" t="n">
-        <v>1.02</v>
+        <v>-1.48</v>
       </c>
       <c r="L2" t="n">
         <v>2.79</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.66</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42102</v>
+        <v>42103</v>
       </c>
       <c r="H3" t="n">
-        <v>206.35</v>
+        <v>213.3</v>
       </c>
       <c r="I3" t="n">
         <v>207.1650165431703</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7</v>
+        <v>-5.13</v>
       </c>
       <c r="L3" t="n">
         <v>6.85</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>9.68</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42122</v>
+        <v>42123</v>
       </c>
       <c r="H4" t="n">
-        <v>206.2</v>
+        <v>202.55</v>
       </c>
       <c r="I4" t="n">
         <v>205.6032015942883</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.33</v>
+        <v>-5.04</v>
       </c>
       <c r="L4" t="n">
-        <v>4.08</v>
+        <v>5.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14</v>
+        <v>0.39</v>
       </c>
       <c r="N4" t="n">
         <v>4.46</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42171</v>
+        <v>42172</v>
       </c>
       <c r="H5" t="n">
-        <v>215.4</v>
+        <v>221.9</v>
       </c>
       <c r="I5" t="n">
         <v>220.6675272993503</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.34</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>8.1</v>
+        <v>10.89</v>
       </c>
       <c r="M5" t="n">
         <v>0.89</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.69</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H6" t="n">
-        <v>238.9</v>
+        <v>235.45</v>
       </c>
       <c r="I6" t="n">
         <v>235.7624314383829</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>7.66</v>
+        <v>6.11</v>
       </c>
       <c r="L6" t="n">
         <v>3.99</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.86</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H7" t="n">
-        <v>214</v>
+        <v>217.75</v>
       </c>
       <c r="I7" t="n">
         <v>214.1348456435063</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" t="n">
-        <v>9.109999999999999</v>
+        <v>7.52</v>
       </c>
       <c r="L7" t="n">
         <v>1.78</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42325</v>
+        <v>42326</v>
       </c>
       <c r="H8" t="n">
-        <v>221.1</v>
+        <v>217.3</v>
       </c>
       <c r="I8" t="n">
         <v>217.3341960419349</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>1.54</v>
+        <v>-0.21</v>
       </c>
       <c r="L8" t="n">
         <v>3.54</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.86</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H9" t="n">
-        <v>230.6</v>
+        <v>235.6</v>
       </c>
       <c r="I9" t="n">
         <v>234.381107336823</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.12</v>
+        <v>-8.42</v>
       </c>
       <c r="L9" t="n">
-        <v>6.53</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>0.78</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H10" t="n">
-        <v>224.2</v>
+        <v>218.25</v>
       </c>
       <c r="I10" t="n">
         <v>219.7963548524434</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.84</v>
+        <v>-7.36</v>
       </c>
       <c r="L10" t="n">
-        <v>5.31</v>
+        <v>7.68</v>
       </c>
       <c r="M10" t="n">
         <v>0.52</v>
       </c>
       <c r="N10" t="n">
-        <v>1.39</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>2.17</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>8.09</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42354</v>
+        <v>42355</v>
       </c>
       <c r="H11" t="n">
-        <v>233.2</v>
+        <v>240.6</v>
       </c>
       <c r="I11" t="n">
         <v>235.9057615813119</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.85</v>
+        <v>-10.24</v>
       </c>
       <c r="L11" t="n">
-        <v>7.81</v>
+        <v>10.84</v>
       </c>
       <c r="M11" t="n">
         <v>0.71</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42389</v>
+        <v>42390</v>
       </c>
       <c r="H12" t="n">
-        <v>239.4</v>
+        <v>234.5</v>
       </c>
       <c r="I12" t="n">
         <v>238.1017119010009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5</v>
+        <v>-2.54</v>
       </c>
       <c r="L12" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="M12" t="n">
         <v>1.21</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H13" t="n">
-        <v>238.65</v>
+        <v>241.4</v>
       </c>
       <c r="I13" t="n">
         <v>239.4890165931762</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.77</v>
+        <v>-2.94</v>
       </c>
       <c r="L13" t="n">
         <v>5.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>8.65</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42487</v>
+        <v>42488</v>
       </c>
       <c r="H14" t="n">
-        <v>242.9</v>
+        <v>237.5</v>
       </c>
       <c r="I14" t="n">
         <v>239.0531490879147</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>0.62</v>
+        <v>-1.62</v>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
         <v>0.65</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42535</v>
+        <v>42536</v>
       </c>
       <c r="H15" t="n">
-        <v>232.65</v>
+        <v>234.6</v>
       </c>
       <c r="I15" t="n">
         <v>234.4949933113077</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="L15" t="n">
         <v>2.27</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.04</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H16" t="n">
-        <v>251.2</v>
+        <v>249.9</v>
       </c>
       <c r="I16" t="n">
         <v>250.4397038694341</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K16" t="n">
-        <v>7.08</v>
+        <v>6.52</v>
       </c>
       <c r="L16" t="n">
         <v>5.2</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.76</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42717</v>
+        <v>42718</v>
       </c>
       <c r="H17" t="n">
-        <v>247.8</v>
+        <v>252.5</v>
       </c>
       <c r="I17" t="n">
         <v>248.2614008849511</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K17" t="n">
-        <v>0.84</v>
+        <v>-1.04</v>
       </c>
       <c r="L17" t="n">
-        <v>0.96</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>1.38</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>5.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42751</v>
+        <v>42752</v>
       </c>
       <c r="H18" t="n">
-        <v>256.5</v>
+        <v>248.1</v>
       </c>
       <c r="I18" t="n">
         <v>248.6781061713671</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>1.58</v>
+        <v>-1.74</v>
       </c>
       <c r="L18" t="n">
         <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.04</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
         <v>1.9</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.47</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42782</v>
+        <v>42783</v>
       </c>
       <c r="H19" t="n">
-        <v>254.4</v>
+        <v>256.3</v>
       </c>
       <c r="I19" t="n">
         <v>255.3918451792395</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.54</v>
+        <v>-3.31</v>
       </c>
       <c r="L19" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="M19" t="n">
         <v>0.51</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42859</v>
+        <v>42860</v>
       </c>
       <c r="H20" t="n">
-        <v>323.6</v>
+        <v>316.5</v>
       </c>
       <c r="I20" t="n">
         <v>318.5890190500053</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K20" t="n">
-        <v>26.26</v>
+        <v>23.49</v>
       </c>
       <c r="L20" t="n">
         <v>1.6</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.85</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42900</v>
+        <v>42901</v>
       </c>
       <c r="H21" t="n">
-        <v>323.5</v>
+        <v>329.8</v>
       </c>
       <c r="I21" t="n">
         <v>328.6225487367664</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.21</v>
+        <v>-4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>3.67</v>
+        <v>5.02</v>
       </c>
       <c r="M21" t="n">
         <v>0.99</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.28</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42975</v>
+        <v>42976</v>
       </c>
       <c r="H22" t="n">
-        <v>373.3</v>
+        <v>365.1</v>
       </c>
       <c r="I22" t="n">
         <v>366.4170046650888</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K22" t="n">
-        <v>13.19</v>
+        <v>10.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.79</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.23</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="H23" t="n">
-        <v>389.05</v>
+        <v>392.1</v>
       </c>
       <c r="I23" t="n">
         <v>391.4858386370017</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.56</v>
+        <v>-7.4</v>
       </c>
       <c r="L23" t="n">
-        <v>6.79</v>
+        <v>7.86</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.09</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H24" t="n">
-        <v>390.85</v>
+        <v>380.9</v>
       </c>
       <c r="I24" t="n">
         <v>384.3285414616185</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.32</v>
+        <v>-2.86</v>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>3.32</v>
       </c>
       <c r="M24" t="n">
         <v>0.37</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H25" t="n">
-        <v>400.4</v>
+        <v>415.95</v>
       </c>
       <c r="I25" t="n">
         <v>402.3329439123864</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.12</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>7.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>1.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.58</v>
+        <v>3.88</v>
       </c>
       <c r="O25" t="n">
         <v>-2.55</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>8.58</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H26" t="n">
-        <v>432.1</v>
+        <v>423.1</v>
       </c>
       <c r="I26" t="n">
         <v>423.2681079145636</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K26" t="n">
-        <v>3.88</v>
+        <v>1.72</v>
       </c>
       <c r="L26" t="n">
         <v>3.51</v>
       </c>
       <c r="M26" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="N26" t="n">
         <v>2.77</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43061</v>
+        <v>43062</v>
       </c>
       <c r="H27" t="n">
-        <v>443.6</v>
+        <v>451.35</v>
       </c>
       <c r="I27" t="n">
         <v>450.458602371185</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.85</v>
+        <v>-6.68</v>
       </c>
       <c r="L27" t="n">
-        <v>5.84</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
         <v>1.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.29</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H28" t="n">
-        <v>449.85</v>
+        <v>431</v>
       </c>
       <c r="I28" t="n">
         <v>441.8115855362835</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.33</v>
+        <v>-4.51</v>
       </c>
       <c r="L28" t="n">
         <v>8.91</v>
       </c>
       <c r="M28" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>2.76</v>
+        <v>4.19</v>
       </c>
       <c r="O28" t="n">
         <v>1.75</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43206</v>
+        <v>43207</v>
       </c>
       <c r="H29" t="n">
-        <v>446.6</v>
+        <v>450</v>
       </c>
       <c r="I29" t="n">
         <v>447.7276008323417</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.62</v>
+        <v>-4.41</v>
       </c>
       <c r="L29" t="n">
         <v>6.15</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.81</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H30" t="n">
-        <v>450.55</v>
+        <v>445.1</v>
       </c>
       <c r="I30" t="n">
         <v>447.2243951975701</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>0.12</v>
+        <v>-1.09</v>
       </c>
       <c r="L30" t="n">
         <v>2.43</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>7.24</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H31" t="n">
-        <v>454.9</v>
+        <v>462.95</v>
       </c>
       <c r="I31" t="n">
         <v>458.2996835890529</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.2</v>
+        <v>-4.01</v>
       </c>
       <c r="L31" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="M31" t="n">
         <v>0.54</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="O31" t="n">
         <v>-1.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H32" t="n">
-        <v>466.6</v>
+        <v>460.3</v>
       </c>
       <c r="I32" t="n">
         <v>463.0230893952275</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>0.79</v>
+        <v>-0.57</v>
       </c>
       <c r="L32" t="n">
         <v>1.74</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.19</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H33" t="n">
-        <v>475.2</v>
+        <v>488.85</v>
       </c>
       <c r="I33" t="n">
         <v>485.1683244430121</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.24</v>
+        <v>-6.2</v>
       </c>
       <c r="L33" t="n">
-        <v>4.41</v>
+        <v>6.5</v>
       </c>
       <c r="M33" t="n">
         <v>0.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.17</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43343</v>
+        <v>43346</v>
       </c>
       <c r="H34" t="n">
-        <v>591.8</v>
+        <v>585.8</v>
       </c>
       <c r="I34" t="n">
         <v>587.9404348061092</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K34" t="n">
-        <v>21.06</v>
+        <v>19.83</v>
       </c>
       <c r="L34" t="n">
         <v>2.51</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.89</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43432</v>
+        <v>43433</v>
       </c>
       <c r="H35" t="n">
-        <v>549.35</v>
+        <v>556.9</v>
       </c>
       <c r="I35" t="n">
         <v>553.6159102842781</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K35" t="n">
-        <v>6.22</v>
+        <v>4.93</v>
       </c>
       <c r="L35" t="n">
         <v>4.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.15</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H36" t="n">
-        <v>540.4</v>
+        <v>519.6</v>
       </c>
       <c r="I36" t="n">
         <v>519.7376848254327</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.96</v>
+        <v>-6.7</v>
       </c>
       <c r="L36" t="n">
-        <v>5.15</v>
+        <v>7.31</v>
       </c>
       <c r="M36" t="n">
-        <v>0.75</v>
+        <v>2.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.73</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>1.37</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43482</v>
+        <v>43483</v>
       </c>
       <c r="H37" t="n">
-        <v>540.7</v>
+        <v>564.45</v>
       </c>
       <c r="I37" t="n">
         <v>550.6901025756736</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.06</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>5.29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.57</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>4.39</v>
       </c>
       <c r="O37" t="n">
         <v>-3.85</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H38" t="n">
-        <v>640.3</v>
+        <v>619.3</v>
       </c>
       <c r="I38" t="n">
         <v>630.1991795937142</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K38" t="n">
-        <v>13.44</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L38" t="n">
         <v>4.15</v>
@@ -2607,7 +3062,7 @@
         <v>1.87</v>
       </c>
       <c r="N38" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="O38" t="n">
         <v>4.39</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43616</v>
+        <v>43619</v>
       </c>
       <c r="H39" t="n">
-        <v>633.95</v>
+        <v>648.3</v>
       </c>
       <c r="I39" t="n">
         <v>642.755523397537</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.37</v>
+        <v>-4.68</v>
       </c>
       <c r="L39" t="n">
         <v>7.12</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.82</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H40" t="n">
-        <v>607.25</v>
+        <v>597.2</v>
       </c>
       <c r="I40" t="n">
         <v>600.422176864553</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.33</v>
+        <v>-7.88</v>
       </c>
       <c r="L40" t="n">
-        <v>7.79</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M40" t="n">
         <v>0.57</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.74</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43686</v>
+        <v>43690</v>
       </c>
       <c r="H41" t="n">
-        <v>553.85</v>
+        <v>607.55</v>
       </c>
       <c r="I41" t="n">
         <v>580.9547539303289</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K41" t="n">
-        <v>7.26</v>
+        <v>-1.73</v>
       </c>
       <c r="L41" t="n">
-        <v>3.75</v>
+        <v>3.97</v>
       </c>
       <c r="M41" t="n">
-        <v>0.82</v>
+        <v>6.11</v>
       </c>
       <c r="N41" t="n">
-        <v>3.87</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>-1.66</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.43</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43823</v>
+        <v>43825</v>
       </c>
       <c r="H42" t="n">
-        <v>737.05</v>
+        <v>722.25</v>
       </c>
       <c r="I42" t="n">
         <v>725.9449501679708</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K42" t="n">
-        <v>21.32</v>
+        <v>18.88</v>
       </c>
       <c r="L42" t="n">
         <v>8.01</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.12</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43874</v>
+        <v>43875</v>
       </c>
       <c r="H43" t="n">
-        <v>702.6</v>
+        <v>709</v>
       </c>
       <c r="I43" t="n">
         <v>708.4132818010075</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K43" t="n">
-        <v>2.72</v>
+        <v>1.83</v>
       </c>
       <c r="L43" t="n">
         <v>6.18</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H44" t="n">
-        <v>675.05</v>
+        <v>663.4</v>
       </c>
       <c r="I44" t="n">
         <v>668.2412050152151</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.79</v>
+        <v>-6.43</v>
       </c>
       <c r="L44" t="n">
-        <v>5.22</v>
+        <v>6.74</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.72</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H45" t="n">
-        <v>513.5</v>
+        <v>574.8</v>
       </c>
       <c r="I45" t="n">
         <v>552.1361976763458</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>22.6</v>
+        <v>13.36</v>
       </c>
       <c r="L45" t="n">
         <v>1.46</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>27.14</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H46" t="n">
-        <v>1027.5</v>
+        <v>1012.6</v>
       </c>
       <c r="I46" t="n">
         <v>1022.345784551076</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K46" t="n">
-        <v>78.76000000000001</v>
+        <v>76.17</v>
       </c>
       <c r="L46" t="n">
         <v>8.789999999999999</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H47" t="n">
-        <v>977.35</v>
+        <v>993.5</v>
       </c>
       <c r="I47" t="n">
         <v>992.9700936230893</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>3.48</v>
+        <v>1.89</v>
       </c>
       <c r="L47" t="n">
         <v>3.17</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.48</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H48" t="n">
-        <v>976.85</v>
+        <v>925.1</v>
       </c>
       <c r="I48" t="n">
         <v>928.6454796824723</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.68</v>
+        <v>-6.88</v>
       </c>
       <c r="L48" t="n">
         <v>11</v>
@@ -3177,7 +3752,7 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>4.19</v>
+        <v>5.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.65</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.34</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44237</v>
+        <v>44238</v>
       </c>
       <c r="H49" t="n">
-        <v>940.95</v>
+        <v>979.75</v>
       </c>
       <c r="I49" t="n">
         <v>978.6150039522969</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.71</v>
+        <v>-5.91</v>
       </c>
       <c r="L49" t="n">
-        <v>4.84</v>
+        <v>6.35</v>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.89</v>
+        <v>4.12</v>
       </c>
       <c r="O49" t="n">
         <v>-5.3</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H50" t="n">
-        <v>979.6</v>
+        <v>957.5</v>
       </c>
       <c r="I50" t="n">
         <v>961.272145005535</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.02</v>
+        <v>-2.27</v>
       </c>
       <c r="L50" t="n">
         <v>4.06</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.06</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44343</v>
+        <v>44344</v>
       </c>
       <c r="H51" t="n">
-        <v>941.8</v>
+        <v>998.4</v>
       </c>
       <c r="I51" t="n">
         <v>967.4756688627955</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K51" t="n">
-        <v>1.64</v>
+        <v>-4.27</v>
       </c>
       <c r="L51" t="n">
         <v>5.01</v>
@@ -3348,7 +3959,7 @@
         <v>1.28</v>
       </c>
       <c r="N51" t="n">
-        <v>3.63</v>
+        <v>6.01</v>
       </c>
       <c r="O51" t="n">
         <v>-2.26</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.41</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44371</v>
+        <v>44372</v>
       </c>
       <c r="H52" t="n">
-        <v>1026.35</v>
+        <v>1003</v>
       </c>
       <c r="I52" t="n">
         <v>1005.545985341617</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K52" t="n">
-        <v>2.8</v>
+        <v>0.46</v>
       </c>
       <c r="L52" t="n">
         <v>5.01</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44420</v>
+        <v>44421</v>
       </c>
       <c r="H53" t="n">
-        <v>1005.9</v>
+        <v>1022.6</v>
       </c>
       <c r="I53" t="n">
         <v>1021.40764620302</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.29</v>
+        <v>-1.95</v>
       </c>
       <c r="L53" t="n">
         <v>2.39</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.88</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H54" t="n">
-        <v>1238.5</v>
+        <v>1208.8</v>
       </c>
       <c r="I54" t="n">
         <v>1222.046121639718</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K54" t="n">
-        <v>21.11</v>
+        <v>18.21</v>
       </c>
       <c r="L54" t="n">
         <v>1.71</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H55" t="n">
-        <v>1170.3</v>
+        <v>1201.55</v>
       </c>
       <c r="I55" t="n">
         <v>1181.208149776067</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K55" t="n">
-        <v>3.18</v>
+        <v>0.6</v>
       </c>
       <c r="L55" t="n">
         <v>2.6</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H56" t="n">
-        <v>1180.95</v>
+        <v>1133.3</v>
       </c>
       <c r="I56" t="n">
         <v>1149.646295000896</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.71</v>
+        <v>-5.68</v>
       </c>
       <c r="L56" t="n">
-        <v>2.74</v>
+        <v>6.58</v>
       </c>
       <c r="M56" t="n">
         <v>1.03</v>
       </c>
       <c r="N56" t="n">
-        <v>1.75</v>
+        <v>4.03</v>
       </c>
       <c r="O56" t="n">
         <v>2.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H57" t="n">
-        <v>1143.4</v>
+        <v>1152.8</v>
       </c>
       <c r="I57" t="n">
         <v>1149.483504768165</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.89</v>
+        <v>-1.72</v>
       </c>
       <c r="L57" t="n">
         <v>5.34</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.93</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H58" t="n">
-        <v>1249</v>
+        <v>1200.2</v>
       </c>
       <c r="I58" t="n">
         <v>1243.085425397999</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K58" t="n">
-        <v>8.34</v>
+        <v>4.11</v>
       </c>
       <c r="L58" t="n">
         <v>3.22</v>
       </c>
       <c r="M58" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="N58" t="n">
-        <v>3.12</v>
+        <v>3.91</v>
       </c>
       <c r="O58" t="n">
         <v>0.82</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.7</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H59" t="n">
-        <v>1227.3</v>
+        <v>1270.05</v>
       </c>
       <c r="I59" t="n">
         <v>1254.213119680259</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.26</v>
+        <v>-5.82</v>
       </c>
       <c r="L59" t="n">
-        <v>5.5</v>
+        <v>6.18</v>
       </c>
       <c r="M59" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="N59" t="n">
         <v>5.83</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44729</v>
+        <v>44732</v>
       </c>
       <c r="H60" t="n">
-        <v>1234.4</v>
+        <v>1212</v>
       </c>
       <c r="I60" t="n">
         <v>1217.702027425619</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.81</v>
+        <v>-4.57</v>
       </c>
       <c r="L60" t="n">
-        <v>4.16</v>
+        <v>5.39</v>
       </c>
       <c r="M60" t="n">
         <v>2.37</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>10.25</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H61" t="n">
-        <v>1227.2</v>
+        <v>1231.85</v>
       </c>
       <c r="I61" t="n">
         <v>1230.067845248616</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.25</v>
+        <v>-1.64</v>
       </c>
       <c r="L61" t="n">
         <v>2.91</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.58</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H62" t="n">
-        <v>1221.4</v>
+        <v>1191.1</v>
       </c>
       <c r="I62" t="n">
         <v>1202.121070735859</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.85</v>
+        <v>-3.31</v>
       </c>
       <c r="L62" t="n">
-        <v>2.28</v>
+        <v>3.62</v>
       </c>
       <c r="M62" t="n">
         <v>2.1</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.7</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H63" t="n">
-        <v>1188.6</v>
+        <v>1191.8</v>
       </c>
       <c r="I63" t="n">
         <v>1190.256201487062</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>0.21</v>
+        <v>-0.06</v>
       </c>
       <c r="L63" t="n">
         <v>2.15</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.25</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H64" t="n">
-        <v>1228.85</v>
+        <v>1222.8</v>
       </c>
       <c r="I64" t="n">
         <v>1224.998770291753</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K64" t="n">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
       <c r="L64" t="n">
         <v>2.71</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.29</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H65" t="n">
-        <v>1108.5</v>
+        <v>1115.9</v>
       </c>
       <c r="I65" t="n">
         <v>1115.567581985388</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K65" t="n">
-        <v>9.35</v>
+        <v>8.74</v>
       </c>
       <c r="L65" t="n">
         <v>2.63</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.16</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H66" t="n">
-        <v>1309.9</v>
+        <v>1269.4</v>
       </c>
       <c r="I66" t="n">
         <v>1274.806105921924</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K66" t="n">
-        <v>17.39</v>
+        <v>13.76</v>
       </c>
       <c r="L66" t="n">
         <v>0.99</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.32</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H67" t="n">
-        <v>1159.85</v>
+        <v>1169.5</v>
       </c>
       <c r="I67" t="n">
         <v>1166.437358471292</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K67" t="n">
-        <v>8.630000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.49</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H68" t="n">
-        <v>1431.5</v>
+        <v>1418.2</v>
       </c>
       <c r="I68" t="n">
         <v>1423.248079136169</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K68" t="n">
-        <v>22.4</v>
+        <v>21.27</v>
       </c>
       <c r="L68" t="n">
         <v>1.75</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.09</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45434</v>
+        <v>45435</v>
       </c>
       <c r="H69" t="n">
-        <v>1460.65</v>
+        <v>1486.05</v>
       </c>
       <c r="I69" t="n">
         <v>1475.353090038855</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.99</v>
+        <v>-4.78</v>
       </c>
       <c r="L69" t="n">
         <v>6.19</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.97</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H70" t="n">
-        <v>1510.3</v>
+        <v>1397.3</v>
       </c>
       <c r="I70" t="n">
         <v>1399.1262467624</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K70" t="n">
-        <v>1.63</v>
+        <v>-5.97</v>
       </c>
       <c r="L70" t="n">
-        <v>4.44</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M70" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>1.11</v>
+        <v>7.48</v>
       </c>
       <c r="O70" t="n">
         <v>1.74</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>11.13</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="H71" t="n">
-        <v>1530.55</v>
+        <v>1565.4</v>
       </c>
       <c r="I71" t="n">
         <v>1532.485973342792</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K71" t="n">
-        <v>-9.539999999999999</v>
+        <v>-12.03</v>
       </c>
       <c r="L71" t="n">
-        <v>10.03</v>
+        <v>13.15</v>
       </c>
       <c r="M71" t="n">
         <v>1.77</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>7.2</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45492</v>
+        <v>45495</v>
       </c>
       <c r="H72" t="n">
-        <v>1555.15</v>
+        <v>1500.7</v>
       </c>
       <c r="I72" t="n">
         <v>1505.506045454937</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.65</v>
+        <v>-4.13</v>
       </c>
       <c r="L72" t="n">
-        <v>2.2</v>
+        <v>4.22</v>
       </c>
       <c r="M72" t="n">
-        <v>0.23</v>
+        <v>1.15</v>
       </c>
       <c r="N72" t="n">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>2.28</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.94</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H73" t="n">
-        <v>1309.15</v>
+        <v>1323.3</v>
       </c>
       <c r="I73" t="n">
         <v>1312.476950470627</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K73" t="n">
-        <v>12.76</v>
+        <v>11.82</v>
       </c>
       <c r="L73" t="n">
         <v>2.6</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>6</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>6.7</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H74" t="n">
-        <v>1253.25</v>
+        <v>1230.45</v>
       </c>
       <c r="I74" t="n">
         <v>1240.468809562504</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.29</v>
+        <v>-7.02</v>
       </c>
       <c r="L74" t="n">
-        <v>6.33</v>
+        <v>7.13</v>
       </c>
       <c r="M74" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="N74" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O74" t="n">
         <v>1.08</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>6.12</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H75" t="n">
-        <v>1266.45</v>
+        <v>1302.35</v>
       </c>
       <c r="I75" t="n">
         <v>1271.599374914377</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.93</v>
+        <v>-5.84</v>
       </c>
       <c r="L75" t="n">
-        <v>3.62</v>
+        <v>7.77</v>
       </c>
       <c r="M75" t="n">
-        <v>0.8</v>
+        <v>4.41</v>
       </c>
       <c r="N75" t="n">
-        <v>1.99</v>
+        <v>2.83</v>
       </c>
       <c r="O75" t="n">
         <v>-1.82</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>5.88</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H76" t="n">
-        <v>1246.3</v>
+        <v>1229.35</v>
       </c>
       <c r="I76" t="n">
         <v>1231.592785961429</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.3</v>
+        <v>-5.61</v>
       </c>
       <c r="L76" t="n">
-        <v>4.52</v>
+        <v>6.32</v>
       </c>
       <c r="M76" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="N76" t="n">
         <v>2.43</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.29</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="H77" t="n">
-        <v>1209.6</v>
+        <v>1249.8</v>
       </c>
       <c r="I77" t="n">
         <v>1235.369676518798</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K77" t="n">
-        <v>1.61</v>
+        <v>-1.66</v>
       </c>
       <c r="L77" t="n">
         <v>4.97</v>
@@ -4830,7 +5753,7 @@
         <v>1.82</v>
       </c>
       <c r="N77" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="O77" t="n">
         <v>-1.36</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>7.73</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H78" t="n">
-        <v>1248.7</v>
+        <v>1204.7</v>
       </c>
       <c r="I78" t="n">
         <v>1227.539117880165</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.09</v>
+        <v>-3.61</v>
       </c>
       <c r="L78" t="n">
-        <v>3.02</v>
+        <v>4.53</v>
       </c>
       <c r="M78" t="n">
         <v>1.45</v>
       </c>
       <c r="N78" t="n">
-        <v>1.76</v>
+        <v>3.52</v>
       </c>
       <c r="O78" t="n">
         <v>3.32</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,25 +5870,25 @@
         <v>7.45</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H79" t="n">
-        <v>1218.95</v>
+        <v>1240.1</v>
       </c>
       <c r="I79" t="n">
         <v>1237.679822555163</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.18</v>
+        <v>-2.94</v>
       </c>
       <c r="L79" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="M79" t="n">
-        <v>0.83</v>
+        <v>2.63</v>
       </c>
       <c r="N79" t="n">
         <v>2.83</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>7.29</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45856</v>
+        <v>45859</v>
       </c>
       <c r="H80" t="n">
-        <v>1476</v>
+        <v>1428.6</v>
       </c>
       <c r="I80" t="n">
         <v>1470.096413940285</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K80" t="n">
-        <v>19.02</v>
+        <v>15.2</v>
       </c>
       <c r="L80" t="n">
         <v>1.01</v>
@@ -5001,7 +5960,7 @@
         <v>1.53</v>
       </c>
       <c r="N80" t="n">
-        <v>2.12</v>
+        <v>3.21</v>
       </c>
       <c r="O80" t="n">
         <v>1.74</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>6.57</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H81" t="n">
-        <v>1398.3</v>
+        <v>1416.8</v>
       </c>
       <c r="I81" t="n">
         <v>1414.069642765091</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K81" t="n">
-        <v>2.12</v>
+        <v>0.83</v>
       </c>
       <c r="L81" t="n">
         <v>3.32</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>4.21</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H82" t="n">
-        <v>1578.1</v>
+        <v>1507.6</v>
       </c>
       <c r="I82" t="n">
         <v>1529.488964872122</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K82" t="n">
-        <v>11.38</v>
+        <v>6.41</v>
       </c>
       <c r="L82" t="n">
         <v>1.25</v>
@@ -5115,7 +6098,7 @@
         <v>0.72</v>
       </c>
       <c r="N82" t="n">
-        <v>1.26</v>
+        <v>4.47</v>
       </c>
       <c r="O82" t="n">
         <v>1.32</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>7.11</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H83" t="n">
-        <v>1458.5</v>
+        <v>1468.7</v>
       </c>
       <c r="I83" t="n">
         <v>1468.127169969031</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K83" t="n">
-        <v>3.26</v>
+        <v>2.58</v>
       </c>
       <c r="L83" t="n">
         <v>4.07</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>6.79</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H84" t="n">
-        <v>1393.9</v>
+        <v>1358</v>
       </c>
       <c r="I84" t="n">
         <v>1369.010182017437</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K84" t="n">
-        <v>-5.09</v>
+        <v>-7.54</v>
       </c>
       <c r="L84" t="n">
-        <v>5.49</v>
+        <v>8.66</v>
       </c>
       <c r="M84" t="n">
-        <v>0.63</v>
+        <v>1.32</v>
       </c>
       <c r="N84" t="n">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
       <c r="O84" t="n">
         <v>0.7</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>6.83</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="H85" t="n">
-        <v>1388.9</v>
+        <v>1425.4</v>
       </c>
       <c r="I85" t="n">
         <v>1408.789691033264</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K85" t="n">
-        <v>-2.28</v>
+        <v>-4.96</v>
       </c>
       <c r="L85" t="n">
         <v>5.6</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5322,22 +6353,22 @@
         <v>7.86</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H86" t="n">
-        <v>1364</v>
+        <v>1358.8</v>
       </c>
       <c r="I86" t="n">
         <v>1361.809377278758</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K86" t="n">
-        <v>-4.31</v>
+        <v>-4.67</v>
       </c>
       <c r="L86" t="n">
-        <v>4.57</v>
+        <v>5.12</v>
       </c>
       <c r="M86" t="n">
         <v>1.15</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,14 @@
       <c r="Q87" t="n">
         <v>116</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10361,7 +11412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.2</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="6">
@@ -10371,7 +11422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -10381,7 +11432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
@@ -10391,7 +11442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -10401,7 +11452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -10411,7 +11462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100.6</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="11">
@@ -10421,7 +11472,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -10431,7 +11482,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -10441,7 +11492,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="14">
@@ -10451,7 +11502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.15</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
@@ -10461,7 +11512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.94</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
@@ -10471,7 +11522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.29</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="17">
@@ -10481,7 +11532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.76000000000001</v>
+        <v>76.17</v>
       </c>
     </row>
     <row r="18">
@@ -10491,7 +11542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.2</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="19">
@@ -10501,7 +11552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.22</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="20">
@@ -10511,7 +11562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.99</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">
@@ -10521,7 +11572,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="22">
@@ -10531,7 +11582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -10541,7 +11592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -10551,7 +11602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="25">
@@ -10561,7 +11612,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.01</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="26">
@@ -10571,7 +11622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="27">
@@ -10591,7 +11642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
